--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_204_R21.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_204_R21.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.3498</v>
+        <v>7.3961</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0096</v>
+        <v>3.3583</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3402</v>
+        <v>4.0377</v>
       </c>
       <c r="G2" t="n">
         <v>1.8503</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5897</v>
+        <v>0.6359</v>
       </c>
       <c r="T2" t="n">
-        <v>2.0331</v>
+        <v>0.3817</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5566</v>
+        <v>0.2541</v>
       </c>
       <c r="V2" t="n">
         <v>2.8223</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>C. OSMAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2426</v>
+        <v>3.7404</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4547</v>
+        <v>1.0466</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7879</v>
+        <v>2.6938</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7966</v>
+        <v>1.1839</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6159</v>
+        <v>2.3349</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1808</v>
+        <v>-1.151</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3034</v>
+        <v>0.6369</v>
       </c>
       <c r="K3" t="n">
-        <v>2.588</v>
+        <v>1.7813</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2845</v>
+        <v>-1.1445</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4932</v>
+        <v>0.5471</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0279</v>
+        <v>0.5536</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4653</v>
+        <v>-0.0065</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3195</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4793</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2709</v>
+        <v>-0.2812</v>
       </c>
       <c r="T3" t="n">
-        <v>0.311</v>
+        <v>-0.1806</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9599</v>
+        <v>-0.1006</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.1444</v>
+        <v>1.214</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. NUNN</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9244</v>
+        <v>3.6371</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1607</v>
+        <v>1.2188</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0851</v>
+        <v>2.4182</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.6735</v>
+        <v>2.7966</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.5741</v>
+        <v>2.6159</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9005</v>
+        <v>0.1808</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9692</v>
+        <v>2.3034</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.9298</v>
+        <v>2.588</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9606</v>
+        <v>-0.2845</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7043</v>
+        <v>0.4932</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6443</v>
+        <v>0.0279</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.06</v>
+        <v>0.4653</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>2.3195</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2473</v>
+        <v>3.4793</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.6653</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6247</v>
+        <v>0.0751</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5421</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>3.7527</v>
+        <v>-2.1444</v>
       </c>
       <c r="W4" t="n">
-        <v>3.7527</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. OSMAN</t>
+          <t>K. NUNN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8311</v>
+        <v>3.3962</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3389</v>
+        <v>0.3111</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4922</v>
+        <v>3.0851</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1839</v>
+        <v>-1.6735</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3349</v>
+        <v>-3.5741</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.151</v>
+        <v>1.9005</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6369</v>
+        <v>-0.9692</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7813</v>
+        <v>-2.9298</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1445</v>
+        <v>1.9606</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5471</v>
+        <v>-0.7043</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5536</v>
+        <v>-0.6443</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0065</v>
+        <v>-0.06</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7834</v>
+        <v>3.2473</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1905</v>
+        <v>0.3892</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8883</v>
+        <v>-0.1529</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3022</v>
+        <v>0.5421</v>
       </c>
       <c r="V5" t="n">
-        <v>1.214</v>
+        <v>3.7527</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7501</v>
+        <v>3.7527</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. YURTSEVEN</t>
+          <t>J. GRANT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6791</v>
+        <v>1.3885</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0538</v>
+        <v>1.6997</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6253</v>
+        <v>-0.3112</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0537</v>
+        <v>0.2918</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8463000000000001</v>
+        <v>1.222</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2074</v>
+        <v>-0.9302</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3566</v>
+        <v>1.8643</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.4671</v>
+        <v>1.6336</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1104</v>
+        <v>0.2308</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.697</v>
+        <v>-1.5725</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3792</v>
+        <v>-0.4116</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3178</v>
+        <v>-1.1609</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1967</v>
+        <v>0.0993</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3383</v>
+        <v>-0.3064</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8584000000000001</v>
+        <v>0.4057</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. GRANT</t>
+          <t>O. YURTSEVEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6307</v>
+        <v>1.2923</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1099</v>
+        <v>0.9359</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4792</v>
+        <v>0.3564</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2918</v>
+        <v>-1.0537</v>
       </c>
       <c r="H7" t="n">
-        <v>1.222</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9302</v>
+        <v>-0.2074</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8643</v>
+        <v>-0.3566</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6336</v>
+        <v>-0.4671</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2308</v>
+        <v>0.1104</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5725</v>
+        <v>-0.697</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4116</v>
+        <v>-0.3792</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.1609</v>
+        <v>-0.3178</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6585</v>
+        <v>0.8098</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8962</v>
+        <v>0.2203</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2377</v>
+        <v>0.5895</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.77</v>
+        <v>0.2231</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.0207</v>
+        <v>-3.4309</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2507</v>
+        <v>3.654</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9671</v>
@@ -1078,13 +1078,13 @@
         <v>2.5515</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.107</v>
+        <v>-0.114</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.963</v>
+        <v>-0.3732</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1441</v>
+        <v>0.2592</v>
       </c>
       <c r="V8" t="n">
         <v>1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3144</v>
+        <v>-1.2472</v>
       </c>
       <c r="E9" t="n">
         <v>-0.0974</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.217</v>
+        <v>-1.1498</v>
       </c>
       <c r="G9" t="n">
         <v>0.3313</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1792</v>
+        <v>-0.112</v>
       </c>
       <c r="T9" t="n">
         <v>-0.224</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V9" t="n">
         <v>-1.4665</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. ROGKAVOPOULOS</t>
+          <t>A. SAMODUROV</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6327</v>
+        <v>-1.5567</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.712</v>
+        <v>-1.2658</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9207</v>
+        <v>-0.2909</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7232</v>
+        <v>-0.3469</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4981</v>
+        <v>-0.5041</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2213</v>
+        <v>0.1573</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1095</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5412</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4317</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8327</v>
+        <v>-0.3469</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0431</v>
+        <v>-0.5041</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7896</v>
+        <v>0.1573</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5544</v>
+        <v>-0.0501</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3383</v>
+        <v>-0.1061</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2161</v>
+        <v>0.056</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SAMODUROV</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7083</v>
+        <v>-1.778</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3838</v>
+        <v>-3.027</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3245</v>
+        <v>1.249</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3469</v>
+        <v>-1.4365</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5041</v>
+        <v>-0.5498</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1573</v>
+        <v>-0.8867</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-1.608</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.4636</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-1.1445</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3469</v>
+        <v>0.1715</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5041</v>
+        <v>-0.0862</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1573</v>
+        <v>0.2578</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2016</v>
+        <v>0.1946</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>-0.2592</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0224</v>
+        <v>0.4538</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>N. ROGKAVOPOULOS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8452</v>
+        <v>-2.1045</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.027</v>
+        <v>-1.1838</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1818</v>
+        <v>-0.9207</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4365</v>
+        <v>-0.7232</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5498</v>
+        <v>0.4981</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8867</v>
+        <v>-1.2213</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.608</v>
+        <v>0.1095</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4636</v>
+        <v>0.5412</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.1445</v>
+        <v>-0.4317</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1715</v>
+        <v>-0.8327</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0862</v>
+        <v>-0.0431</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2578</v>
+        <v>-0.7896</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1274</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2592</v>
+        <v>-0.1336</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3866</v>
+        <v>0.2161</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5361</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.3871</v>
+        <v>14.38730000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.4346999999999994</v>
+        <v>-0.4345000000000006</v>
       </c>
       <c r="F13" t="n">
-        <v>14.8218</v>
+        <v>14.8216</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2530000000000003</v>
+        <v>0.253</v>
       </c>
       <c r="H13" t="n">
         <v>1.8421</v>
@@ -1444,7 +1444,7 @@
         <v>2.0049</v>
       </c>
       <c r="K13" t="n">
-        <v>2.758499999999999</v>
+        <v>2.7585</v>
       </c>
       <c r="L13" t="n">
         <v>-0.7537000000000001</v>
@@ -1453,13 +1453,13 @@
         <v>-1.7516</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9161999999999999</v>
+        <v>-0.9161999999999998</v>
       </c>
       <c r="O13" t="n">
         <v>-0.8352000000000002</v>
       </c>
       <c r="P13" t="n">
-        <v>6.9586</v>
+        <v>6.958600000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-11.5978</v>
@@ -1468,16 +1468,16 @@
         <v>18.5562</v>
       </c>
       <c r="S13" t="n">
-        <v>2.319700000000001</v>
+        <v>2.3194</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0587</v>
+        <v>-1.0589</v>
       </c>
       <c r="U13" t="n">
-        <v>3.3783</v>
+        <v>3.3781</v>
       </c>
       <c r="V13" t="n">
-        <v>4.855999999999998</v>
+        <v>4.855999999999999</v>
       </c>
       <c r="W13" t="n">
         <v>10.217</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7298</v>
+        <v>4.3322</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3185</v>
+        <v>3.2005</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4113</v>
+        <v>1.1316</v>
       </c>
       <c r="G14" t="n">
         <v>2.5065</v>
@@ -1546,13 +1546,13 @@
         <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>0.597</v>
+        <v>0.1994</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0351</v>
+        <v>-0.1531</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6322</v>
+        <v>0.3525</v>
       </c>
       <c r="V14" t="n">
         <v>0.9304</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4084</v>
+        <v>3.9366</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9988</v>
+        <v>2.527</v>
       </c>
       <c r="F15" t="n">
         <v>1.4095</v>
@@ -1624,10 +1624,10 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3971</v>
+        <v>-0.0747</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1221</v>
+        <v>-0.3497</v>
       </c>
       <c r="U15" t="n">
         <v>0.275</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9475</v>
+        <v>2.2506</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3894</v>
+        <v>0.6253</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5581</v>
+        <v>1.6253</v>
       </c>
       <c r="G16" t="n">
         <v>2.8972</v>
@@ -1702,13 +1702,13 @@
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4859</v>
+        <v>-0.1828</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.963</v>
+        <v>-0.727</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4771</v>
+        <v>0.5443</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5086000000000001</v>
+        <v>-0.1218</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2443</v>
+        <v>-2.1264</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7357</v>
+        <v>2.0046</v>
       </c>
       <c r="G17" t="n">
         <v>0.4561</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9647</v>
+        <v>-0.5779</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6721</v>
+        <v>-0.5542</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2926</v>
+        <v>-0.0237</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.392</v>
+        <v>-1.468</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8115</v>
+        <v>-0.1637</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5805</v>
+        <v>-1.3043</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5756</v>
+        <v>0.1227</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8501</v>
+        <v>-0.3624</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2745</v>
+        <v>0.4851</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5115</v>
+        <v>1.7674</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6757</v>
+        <v>0.911</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1642</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0641</v>
+        <v>-1.6447</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1744</v>
+        <v>-1.2734</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1103</v>
+        <v>-0.3713</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6959</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3365</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4604</v>
+        <v>-0.4518</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1239</v>
+        <v>0.5364</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6083</v>
+        <v>-0.2836</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.1444</v>
+        <v>-1.3558</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9119</v>
+        <v>-1.7738</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5175</v>
+        <v>-1.2833</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3944</v>
+        <v>-0.4905</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1227</v>
+        <v>0.5756</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3624</v>
+        <v>0.8501</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4851</v>
+        <v>-0.2745</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7674</v>
+        <v>0.5115</v>
       </c>
       <c r="K19" t="n">
-        <v>0.911</v>
+        <v>0.6757</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8564000000000001</v>
+        <v>-0.1642</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6447</v>
+        <v>0.0641</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.2734</v>
+        <v>0.1744</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3713</v>
+        <v>-0.1103</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.3917</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.5515</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3593</v>
+        <v>-0.0452</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8057</v>
+        <v>-0.0114</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4463</v>
+        <v>-0.0338</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2836</v>
+        <v>-1.6083</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.3558</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5545</v>
+        <v>-3.5542</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.3976</v>
+        <v>-1.4729</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8431</v>
+        <v>-2.0813</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1411</v>
+        <v>-1.5287</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6025</v>
+        <v>-0.6253</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5386</v>
+        <v>-0.9034</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.5948</v>
+        <v>-0.0341</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.9557</v>
+        <v>0.605</v>
       </c>
       <c r="L20" t="n">
         <v>-0.6391</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4537</v>
+        <v>-1.4945</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3532</v>
+        <v>-1.2303</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1005</v>
+        <v>-0.2643</v>
       </c>
       <c r="P20" t="n">
         <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0505</v>
+        <v>-0.0255</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4832</v>
+        <v>-0.047</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.0215</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9917</v>
+        <v>-3.7162</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.7088</v>
+        <v>-5.2796</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.283</v>
+        <v>1.5635</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.5287</v>
+        <v>-2.1411</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6253</v>
+        <v>-1.6025</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9034</v>
+        <v>-0.5386</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0341</v>
+        <v>-2.5948</v>
       </c>
       <c r="K21" t="n">
-        <v>0.605</v>
+        <v>-1.9557</v>
       </c>
       <c r="L21" t="n">
         <v>-0.6391</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4945</v>
+        <v>0.4537</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2303</v>
+        <v>0.3532</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2643</v>
+        <v>0.1005</v>
       </c>
       <c r="P21" t="n">
         <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3917</v>
+        <v>-2.3195</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.463</v>
+        <v>-0.1111</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2829</v>
+        <v>-0.3653</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1801</v>
+        <v>0.2541</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2278</v>
+        <v>-3.9697</v>
       </c>
       <c r="E22" t="n">
         <v>-3.8178</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.41</v>
+        <v>-0.1519</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0477</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8606</v>
+        <v>-0.6025</v>
       </c>
       <c r="T22" t="n">
         <v>-0.4753</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3853</v>
+        <v>-0.1272</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6208</v>
+        <v>-4.234</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.393</v>
+        <v>-2.2751</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2278</v>
+        <v>-1.9589</v>
       </c>
       <c r="G23" t="n">
         <v>-3.5839</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9647</v>
+        <v>-0.5779</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3576</v>
+        <v>-0.2396</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6071</v>
+        <v>-0.3383</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2654</v>
+        <v>-5.2826</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6378</v>
+        <v>-4.7557</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6277</v>
+        <v>-0.5268</v>
       </c>
       <c r="G24" t="n">
         <v>-2.0573</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3976</v>
+        <v>0.3804</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1142</v>
+        <v>-0.0037</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2834</v>
+        <v>0.3842</v>
       </c>
       <c r="V24" t="n">
         <v>-1.7501</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.387</v>
+        <v>-13.6009</v>
       </c>
       <c r="E25" t="n">
-        <v>-14.8216</v>
+        <v>-14.8217</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4343000000000002</v>
+        <v>1.2208</v>
       </c>
       <c r="G25" t="n">
         <v>-0.2531999999999974</v>
@@ -2404,13 +2404,13 @@
         <v>11.5978</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.3195</v>
+        <v>-1.5332</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.3782</v>
+        <v>-3.3781</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0588</v>
+        <v>1.845</v>
       </c>
       <c r="V25" t="n">
         <v>-4.856000000000001</v>
